--- a/results/reference_coronary.xlsx
+++ b/results/reference_coronary.xlsx
@@ -1,20 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Semester_1-Period_2\P2-ImgHeart\IMG-Heart\results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6286AB3-5190-42E0-AAB9-6EF7CF314D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReferenceTables" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>Measurement</t>
   </si>
@@ -25,62 +42,56 @@
     <t>SD</t>
   </si>
   <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>Q3</t>
-  </si>
-  <si>
-    <t>--- BIFURCATION ---</t>
-  </si>
-  <si>
-    <t>LEFT MAIN DIAM., MM</t>
-  </si>
-  <si>
     <t>LAD DIAM., MM</t>
   </si>
   <si>
     <t>LCX DIAM., MM</t>
   </si>
   <si>
-    <t>ANGLE A, °</t>
-  </si>
-  <si>
-    <t>ANGLE B, °</t>
-  </si>
-  <si>
-    <t>ANGLE C, °</t>
-  </si>
-  <si>
-    <t>INFLOW ANGLE, °</t>
-  </si>
-  <si>
-    <t>LEFT MAIN LENGTH, MM</t>
-  </si>
-  <si>
-    <t>--- TRIFURCATION ---</t>
-  </si>
-  <si>
-    <t>INT. DIAM., MM</t>
-  </si>
-  <si>
-    <t>ANGLE B1, °</t>
-  </si>
-  <si>
-    <t>ANGLE B2, °</t>
-  </si>
-  <si>
-    <t>ANGLE D, °</t>
+    <t xml:space="preserve">TRIFURCATION </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BIFURCATION </t>
+  </si>
+  <si>
+    <t>ANGLE A</t>
+  </si>
+  <si>
+    <t>ANGLE B</t>
+  </si>
+  <si>
+    <t>ANGLE C</t>
+  </si>
+  <si>
+    <t>INFLOW ANGLE</t>
+  </si>
+  <si>
+    <t>LEFT MAIN LENGTH</t>
+  </si>
+  <si>
+    <t>LEFT MAIN DIAM</t>
+  </si>
+  <si>
+    <t>LAD DIAM</t>
+  </si>
+  <si>
+    <t>LCX DIAM</t>
+  </si>
+  <si>
+    <t>INT. DIAM</t>
+  </si>
+  <si>
+    <t>ANGLE B1</t>
+  </si>
+  <si>
+    <t>ANGLE B2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,13 +154,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +206,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -221,6 +240,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -255,9 +275,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -430,11 +451,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -444,24 +468,15 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -469,19 +484,10 @@
       <c r="C3">
         <v>0.8</v>
       </c>
-      <c r="D3">
-        <v>3.2</v>
-      </c>
-      <c r="E3">
-        <v>3.6</v>
-      </c>
-      <c r="F3">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>3.2</v>
@@ -489,19 +495,10 @@
       <c r="C4">
         <v>0.7</v>
       </c>
-      <c r="D4">
-        <v>2.8</v>
-      </c>
-      <c r="E4">
-        <v>3.2</v>
-      </c>
-      <c r="F4">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -509,19 +506,10 @@
       <c r="C5">
         <v>0.7</v>
       </c>
-      <c r="D5">
-        <v>2.5</v>
-      </c>
-      <c r="E5">
-        <v>3.1</v>
-      </c>
-      <c r="F5">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>126.7</v>
@@ -529,19 +517,10 @@
       <c r="C6">
         <v>21.4</v>
       </c>
-      <c r="D6">
-        <v>115.8</v>
-      </c>
-      <c r="E6">
-        <v>129.8</v>
-      </c>
-      <c r="F6">
-        <v>141.6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>75.2</v>
@@ -549,19 +528,10 @@
       <c r="C7">
         <v>23.3</v>
       </c>
-      <c r="D7">
-        <v>61.4</v>
-      </c>
-      <c r="E7">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="F7">
-        <v>88.90000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>138.6</v>
@@ -569,64 +539,37 @@
       <c r="C8">
         <v>20</v>
       </c>
-      <c r="D8">
-        <v>132</v>
-      </c>
-      <c r="E8">
-        <v>140.2</v>
-      </c>
-      <c r="F8">
-        <v>150.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>8.300000000000001</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="C9">
         <v>24.6</v>
       </c>
-      <c r="D9">
-        <v>-8.1</v>
-      </c>
-      <c r="E9">
-        <v>10.4</v>
-      </c>
-      <c r="F9">
-        <v>25.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="C10">
         <v>5.6</v>
       </c>
-      <c r="D10">
-        <v>7</v>
-      </c>
-      <c r="E10">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>3.5</v>
@@ -634,19 +577,10 @@
       <c r="C13">
         <v>0.8</v>
       </c>
-      <c r="D13">
-        <v>3</v>
-      </c>
-      <c r="E13">
-        <v>3.6</v>
-      </c>
-      <c r="F13">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>3.1</v>
@@ -654,19 +588,10 @@
       <c r="C14">
         <v>0.9</v>
       </c>
-      <c r="D14">
-        <v>2.4</v>
-      </c>
-      <c r="E14">
-        <v>3.3</v>
-      </c>
-      <c r="F14">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>2.9</v>
@@ -674,19 +599,10 @@
       <c r="C15">
         <v>0.8</v>
       </c>
-      <c r="D15">
-        <v>2.4</v>
-      </c>
-      <c r="E15">
-        <v>2.9</v>
-      </c>
-      <c r="F15">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>2.6</v>
@@ -694,19 +610,10 @@
       <c r="C16">
         <v>0.5</v>
       </c>
-      <c r="D16">
-        <v>2.1</v>
-      </c>
-      <c r="E16">
-        <v>2.5</v>
-      </c>
-      <c r="F16">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B17">
         <v>120</v>
@@ -714,39 +621,21 @@
       <c r="C17">
         <v>18.5</v>
       </c>
-      <c r="D17">
-        <v>112.6</v>
-      </c>
-      <c r="E17">
-        <v>118.1</v>
-      </c>
-      <c r="F17">
-        <v>130.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>58.4</v>
       </c>
       <c r="C18">
-        <v>19.4</v>
-      </c>
-      <c r="D18">
-        <v>41.4</v>
-      </c>
-      <c r="E18">
-        <v>60</v>
-      </c>
-      <c r="F18">
-        <v>72.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>46.1</v>
@@ -754,39 +643,21 @@
       <c r="C19">
         <v>14.5</v>
       </c>
-      <c r="D19">
-        <v>35.4</v>
-      </c>
-      <c r="E19">
-        <v>45.4</v>
-      </c>
-      <c r="F19">
-        <v>56.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B20">
-        <v>88.59999999999999</v>
+        <v>88.6</v>
       </c>
       <c r="C20">
         <v>21.1</v>
       </c>
-      <c r="D20">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="E20">
-        <v>89</v>
-      </c>
-      <c r="F20">
-        <v>100.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B21">
         <v>136.6</v>
@@ -794,74 +665,27 @@
       <c r="C21">
         <v>14.1</v>
       </c>
-      <c r="D21">
-        <v>127.7</v>
-      </c>
-      <c r="E21">
-        <v>137.6</v>
-      </c>
-      <c r="F21">
-        <v>147.6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B22">
-        <v>141.8</v>
+        <v>14.6</v>
       </c>
       <c r="C22">
-        <v>22.4</v>
-      </c>
-      <c r="D22">
-        <v>130.7</v>
-      </c>
-      <c r="E22">
-        <v>142.6</v>
-      </c>
-      <c r="F22">
-        <v>158.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B23">
-        <v>14.6</v>
+        <v>11.3</v>
       </c>
       <c r="C23">
-        <v>23.8</v>
-      </c>
-      <c r="D23">
-        <v>-3.9</v>
-      </c>
-      <c r="E23">
-        <v>20</v>
-      </c>
-      <c r="F23">
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24">
-        <v>11.3</v>
-      </c>
-      <c r="C24">
-        <v>4.4</v>
-      </c>
-      <c r="D24">
-        <v>8</v>
-      </c>
-      <c r="E24">
-        <v>10</v>
-      </c>
-      <c r="F24">
-        <v>14</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
   </sheetData>
